--- a/catalog/units.xlsx
+++ b/catalog/units.xlsx
@@ -460,7 +460,11 @@
           <t>قطعه</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>piece,pieces,pc,pcs,قطعة,حبة,بالقطعة</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -474,7 +478,11 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kg,kilo,kilogram,كجم,كيلو</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -488,7 +496,11 @@
           <t>غرام</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>g,gram,grams,gr,جم,غرام</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -502,7 +514,11 @@
           <t>فرط</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>فرط,bunch</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -516,7 +532,11 @@
           <t>حزمة</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>حزمة,pack,bundle</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -530,7 +550,11 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ml,مل,milliliter,millilitre</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/catalog/units.xlsx
+++ b/catalog/units.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,6 +556,114 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>قطعه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>piece,pieces,pc,pcs,قطعة,حبة,بالقطعة</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>kg,kilo,kilogram,كجم,كيلو</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>غرام</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>g,gram,grams,gr,جم,غرام</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>فرط</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>فرط,bunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>حزمة</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>حزمة,pack,bundle</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ml,مل,milliliter,millilitre</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
